--- a/output/casestudy_20260821.xlsx
+++ b/output/casestudy_20260821.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.431672799999433</v>
+        <v>4.58949500000017</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.302103199999692</v>
+        <v>4.386880999998539</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.412567899998976</v>
+        <v>4.773244299998623</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.427865600000587</v>
+        <v>4.85554989999946</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.44992209999873</v>
+        <v>4.666030500000488</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.477843799999391</v>
+        <v>5.055965100000321</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.4 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.3 초</t>
+          <t>4.4 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.4 초</t>
+          <t>4.8 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.4 초</t>
+          <t>4.9 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.4 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.5 초</t>
+          <t>5.1 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27.5 초</t>
+          <t>29.4 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260821.xlsx
+++ b/output/casestudy_20260821.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.58949500000017</v>
+        <v>4.657522999998037</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.386880999998539</v>
+        <v>4.488954399999784</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.773244299998623</v>
+        <v>4.462434400000348</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.85554989999946</v>
+        <v>4.639236800001527</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.666030500000488</v>
+        <v>4.744109000002936</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.055965100000321</v>
+        <v>4.690322499998729</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.4 초</t>
+          <t>4.5 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>4.5 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.9 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.1 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29.4 초</t>
+          <t>28.7 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260821.xlsx
+++ b/output/casestudy_20260821.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.657522999998037</v>
+        <v>4.953271200000017</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.488954399999784</v>
+        <v>4.762160599999333</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.462434400000348</v>
+        <v>4.733253700000205</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.639236800001527</v>
+        <v>4.583061699999234</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.744109000002936</v>
+        <v>4.810313599999063</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.690322499998729</v>
+        <v>4.749925600001006</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>5.0 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.5 초</t>
+          <t>4.8 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.5 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>4.8 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28.7 초</t>
+          <t>29.7 초</t>
         </is>
       </c>
     </row>
